--- a/data/trans_dic/IP31KM15_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM15_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>52,27%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>41,11; 58,66</t>
+          <t>44,75; 61,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41,73; 60,28</t>
+          <t>43,8; 59,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44,99; 57,49</t>
+          <t>46,71; 58,06</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>62,18%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>56,49; 72,44</t>
+          <t>50,22; 68,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>49,76; 67,32</t>
+          <t>56,26; 73,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,81; 67,71</t>
+          <t>56,12; 68,17</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,74%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>55,66; 78,97</t>
+          <t>47,66; 70,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46,54; 69,28</t>
+          <t>51,19; 77,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53,62; 70,45</t>
+          <t>52,76; 70,53</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>56,79%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33,28; 58,4</t>
+          <t>51,18; 65,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>49,4; 63,82</t>
+          <t>47,88; 61,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42,66; 58,4</t>
+          <t>52,25; 62,01</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>55,23%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>49,16; 65,34</t>
+          <t>42,77; 63,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>44,06; 62,66</t>
+          <t>52,37; 67,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48,44; 61,56</t>
+          <t>49,46; 61,93</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>52,81%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>50,46; 69,73</t>
+          <t>34,54; 57,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32,8; 53,87</t>
+          <t>49,01; 69,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>44,09; 59,34</t>
+          <t>45,09; 60,31</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>56,55%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>47,89; 60,13</t>
+          <t>50,76; 58,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>50,17; 57,91</t>
+          <t>54,88; 61,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51,13; 57,72</t>
+          <t>54,04; 59,11</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>78</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>50806</t>
+          <t>64145</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>70009</t>
+          <t>51653</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120815</t>
+          <t>115798</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>41809; 59661</t>
+          <t>54238; 73984</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>56411; 81481</t>
+          <t>43950; 59812</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>106580; 136183</t>
+          <t>103495; 128647</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>89</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>60246</t>
+          <t>53523</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>55029</t>
+          <t>61686</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>115275</t>
+          <t>115209</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52758; 67657</t>
+          <t>45134; 61781</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46625; 63084</t>
+          <t>53679; 69657</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>104429; 126693</t>
+          <t>103992; 126305</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>51</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33701</t>
+          <t>33466</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36302</t>
+          <t>34197</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70002</t>
+          <t>67663</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27882; 39555</t>
+          <t>26617; 39135</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29013; 43186</t>
+          <t>26626; 40046</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>60284; 79207</t>
+          <t>56904; 76067</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>104154</t>
+          <t>114875</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>121638</t>
+          <t>97504</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>225792</t>
+          <t>212378</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71720; 125882</t>
+          <t>100978; 128717</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>105058; 135710</t>
+          <t>84567; 108422</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>182658; 250049</t>
+          <t>195391; 231901</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>102</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>67134</t>
+          <t>75207</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>83164</t>
+          <t>68965</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>150298</t>
+          <t>144172</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>56790; 75470</t>
+          <t>62263; 91826</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>70263; 99915</t>
+          <t>60474; 77771</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>133191; 169271</t>
+          <t>129124; 161676</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>56</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>41576</t>
+          <t>29798</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>29735</t>
+          <t>42141</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>71310</t>
+          <t>71940</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>34764; 48039</t>
+          <t>22752; 37616</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22645; 37187</t>
+          <t>34483; 48792</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>60809; 81842</t>
+          <t>61418; 82155</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>528</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>492</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>357616</t>
+          <t>371014</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>395876</t>
+          <t>356147</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>753492</t>
+          <t>727161</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>308968; 387917</t>
+          <t>342953; 394890</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>367452; 424124</t>
+          <t>334907; 377364</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>704307; 795024</t>
+          <t>694942; 760048</t>
         </is>
       </c>
     </row>
